--- a/db/clientes.xlsx
+++ b/db/clientes.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="18.77734375" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -866,6 +866,86 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>larissa</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>98085</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>larissa.feia@gmail.com</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>988094</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>jgpjfjg</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> oiiiii</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Larissa Feia</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>98085</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>larissa.feia@gmail.com</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>988094</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>jgpjfjg</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> kknn</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/db/clientes.xlsx
+++ b/db/clientes.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="18.77734375" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -946,6 +946,46 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Larissa Feia</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>90809808</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>larissa.feia@gmail.com</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>99089</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>jgpjfjg</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> flkjfglkj</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
